--- a/backend/app/data/updated_scheduling_data.xlsx
+++ b/backend/app/data/updated_scheduling_data.xlsx
@@ -913,7 +913,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="3">
@@ -3595,6 +3595,58 @@
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>https://meet.onboardiq.io/session/pNt8Yi7y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Prathamesh</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>HR Introduction</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Shivani</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11 Apr</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>HR Admin</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09 07:40:40 UTC</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>https://meet.onboardiq.io/session/dkro0X7A</t>
         </is>
       </c>
     </row>

--- a/backend/app/data/updated_scheduling_data.xlsx
+++ b/backend/app/data/updated_scheduling_data.xlsx
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="3">
@@ -3647,6 +3647,214 @@
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>https://meet.onboardiq.io/session/dkro0X7A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Anurag Mandlekar</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>HR Introduction</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Gaurav</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13 Apr</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>HR Admin</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13 08:23:22 UTC</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>https://meet.onboardiq.io/session/Yl740LrF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Anurag Mandlekar</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Manager Introduction</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Prathamesh</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10 Apr</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>HR Admin</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13 08:24:09 UTC</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>https://meet.onboardiq.io/session/WvhzSu99</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Tejas</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>HR Introduction</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Priti</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11 Apr</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>HR Admin</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13 09:30:29 UTC</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>https://meet.onboardiq.io/session/ZVkNRrKd</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Tejas</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Delivery Head Introduction</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Kaustubh</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Delivery Head</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12 Apr</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>HR Admin</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13 09:59:03 UTC</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>https://meet.onboardiq.io/session/G4Og6a23</t>
         </is>
       </c>
     </row>

--- a/backend/app/data/updated_scheduling_data.xlsx
+++ b/backend/app/data/updated_scheduling_data.xlsx
@@ -1201,7 +1201,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="3">
@@ -3855,6 +3855,58 @@
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>https://meet.onboardiq.io/session/G4Og6a23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Vaidehi</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>HR Introduction</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Ketaki</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12 Apr</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>HR Admin</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14 06:57:23 UTC</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>https://meet.onboardiq.io/session/g0nDFA1j</t>
         </is>
       </c>
     </row>

--- a/backend/app/data/updated_scheduling_data.xlsx
+++ b/backend/app/data/updated_scheduling_data.xlsx
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="3">
@@ -3907,6 +3907,58 @@
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>https://meet.onboardiq.io/session/g0nDFA1j</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Vaidehi</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Manager Introduction</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Harshada</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11 Apr</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>02:00 PM</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>HR Admin</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-14 08:04:10 UTC</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>https://meet.onboardiq.io/session/lM33oMSQ</t>
         </is>
       </c>
     </row>

--- a/backend/app/data/updated_scheduling_data.xlsx
+++ b/backend/app/data/updated_scheduling_data.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="3">
@@ -3959,6 +3959,58 @@
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>https://meet.onboardiq.io/session/lM33oMSQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Tejas Ninawe</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>HR Introduction</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Mohini</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10 Apr</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>HR Admin</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15 05:21:08 UTC</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>https://meet.onboardiq.io/session/GCWPSoNW</t>
         </is>
       </c>
     </row>
